--- a/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
+++ b/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A789A36B-610F-4F64-BA37-96262CAFB538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CA6448-A89E-416D-9058-33AFD07A5C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61260" yWindow="1725" windowWidth="24900" windowHeight="14490" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="74">
   <si>
     <t>Source:</t>
   </si>
@@ -541,6 +541,12 @@
   </si>
   <si>
     <t>A smaller share of iron is produced globally by the direct reduced iron (DRI) process.</t>
+  </si>
+  <si>
+    <t>green hydrogen if</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -638,7 +644,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2152,7 +2158,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -2243,6 +2249,22 @@
         <v>13</v>
       </c>
       <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -2256,7 +2278,7 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -2350,6 +2372,22 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
+++ b/InputData/indst/IFSR/Industrial Fuel Shifting Ratio.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\indst\IFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CA6448-A89E-416D-9058-33AFD07A5C19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9D3BB9-8DB3-4EA5-B675-6B1B020005E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61260" yWindow="1725" windowWidth="24900" windowHeight="14490" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9405" yWindow="810" windowWidth="19110" windowHeight="16425" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Calcs" sheetId="4" r:id="rId2"/>
     <sheet name="HPEbP" sheetId="5" r:id="rId3"/>
     <sheet name="IFSR-chemicals" sheetId="3" r:id="rId4"/>
-    <sheet name="ISFR-ironsteel" sheetId="6" r:id="rId5"/>
+    <sheet name="IFSR-ironsteel" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="72">
   <si>
     <t>Source:</t>
   </si>
@@ -541,12 +541,6 @@
   </si>
   <si>
     <t>A smaller share of iron is produced globally by the direct reduced iron (DRI) process.</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -951,14 +945,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -966,188 +960,188 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>70</v>
       </c>
@@ -1161,12 +1155,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C6A4AC5-8865-4921-8E10-BDED8AECA8F6}">
   <dimension ref="A2:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1174,7 +1168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1185,7 +1179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1196,7 +1190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -1207,12 +1201,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1223,7 +1217,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1234,7 +1228,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1245,12 +1239,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1261,12 +1255,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1275,7 +1269,7 @@
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6"/>
     </row>
   </sheetData>
@@ -1286,13 +1280,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221F3C08-152C-483E-8BAD-E349F8D44D7B}">
   <dimension ref="A1:AI8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1399,7 +1393,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1506,7 +1500,7 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1613,7 +1607,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1720,7 +1714,7 @@
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1827,7 +1821,7 @@
         <v>0.46274509803921571</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1934,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -2041,7 +2035,7 @@
         <v>0.77521306818181679</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2158,19 +2152,19 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2178,7 +2172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2187,7 +2181,7 @@
         <v>0.57004830917874394</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2196,7 +2190,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2204,7 +2198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2212,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2220,7 +2214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2228,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2236,7 +2230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2244,27 +2238,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
         <v>1</v>
       </c>
     </row>
@@ -2278,19 +2256,19 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2298,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2307,7 +2285,7 @@
         <v>0.5371573604060913</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2316,7 +2294,7 @@
         <v>0.71951219512195119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2324,7 +2302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2332,7 +2310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2340,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2348,7 +2326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2356,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2364,27 +2342,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13">
         <v>1</v>
       </c>
     </row>
